--- a/contenus/tab2/exs3-recherchev-valorisation.xlsx
+++ b/contenus/tab2/exs3-recherchev-valorisation.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consignes" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exercice" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Correction" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -931,329 +930,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Référence</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Quantité en stock</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Prix unitaire (€)</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Valeur du stock (€)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>REF201</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>50</v>
-      </c>
-      <c r="C2">
-        <f>VLOOKUP(A2,$F$2:$G$13,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="D2">
-        <f>B2*C2</f>
-        <v/>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>REF201</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>REF203</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <f>VLOOKUP(A3,$F$2:$G$13,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="D3">
-        <f>B3*C3</f>
-        <v/>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>REF202</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>REF205</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>20</v>
-      </c>
-      <c r="C4">
-        <f>VLOOKUP(A4,$F$2:$G$13,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="D4">
-        <f>B4*C4</f>
-        <v/>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>REF203</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>REF207</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>100</v>
-      </c>
-      <c r="C5">
-        <f>VLOOKUP(A5,$F$2:$G$13,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="D5">
-        <f>B5*C5</f>
-        <v/>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>REF204</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>REF209</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>60</v>
-      </c>
-      <c r="C6">
-        <f>VLOOKUP(A6,$F$2:$G$13,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="D6">
-        <f>B6*C6</f>
-        <v/>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>REF205</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>22.9</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>REF211</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>300</v>
-      </c>
-      <c r="C7">
-        <f>VLOOKUP(A7,$F$2:$G$13,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="D7">
-        <f>B7*C7</f>
-        <v/>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>REF206</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>REF202</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>80</v>
-      </c>
-      <c r="C8">
-        <f>VLOOKUP(A8,$F$2:$G$13,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="D8">
-        <f>B8*C8</f>
-        <v/>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>REF207</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>5.1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>REF204</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>150</v>
-      </c>
-      <c r="C9">
-        <f>VLOOKUP(A9,$F$2:$G$13,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="D9">
-        <f>B9*C9</f>
-        <v/>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>REF208</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>REF206</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>10</v>
-      </c>
-      <c r="C10">
-        <f>VLOOKUP(A10,$F$2:$G$13,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="D10">
-        <f>B10*C10</f>
-        <v/>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>REF209</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>9.800000000000001</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>REF208</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>3</v>
-      </c>
-      <c r="C11">
-        <f>VLOOKUP(A11,$F$2:$G$13,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="D11">
-        <f>B11*C11</f>
-        <v/>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>REF210</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>45.5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>REF211</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>2.3</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="D13">
-        <f>SUM(D2:D11)</f>
-        <v/>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>REF212</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>75</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>